--- a/templates/valuation_template.xlsx
+++ b/templates/valuation_template.xlsx
@@ -138,11 +138,11 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -273,9 +273,49 @@
     <author>template</author>
   </authors>
   <commentList>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: macro.risk_free_rate</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: industry.equity_risk_premium</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: industry.levered_beta</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: macro.baa_corporate_yield</t>
+      </text>
+    </comment>
     <comment ref="B8" authorId="0" shapeId="0">
       <text>
         <t>Pipeline field: tax.effective_rate</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: industry.pretax_operating_margin</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: industry.sales_to_capital</t>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: industry.cost_of_capital</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: industry.return_on_invested_capital</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0" shapeId="0">
@@ -1375,7 +1415,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Tune to current yield as of valuation date.</t>
+          <t>Sourced from macro feed; override to lock.</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1430,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Implied ERP; refresh quarterly from a standard source.</t>
+          <t>Sourced from industry feed (implied ERP); override to lock.</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1445,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Bottom-up: weighted avg of segment betas if multi-business.</t>
+          <t>Sourced from industry feed; bottom-up override is appropriate for multi-business issuers.</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1460,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>rf + spread implied by credit rating.</t>
+          <t>Sourced from macro feed (BAA corp yield); refine by credit rating.</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1470,7 @@
           <t>Marginal tax rate</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1445,7 +1485,7 @@
           <t>Effective tax rate (current)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Provision / pre-tax income — pipeline pulls from filing.</t>
@@ -1468,12 +1508,12 @@
           <t>Compounded revenue growth, Y1-Y5</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="10" t="n">
         <v>0.08</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Glide path to terminal. Tune for thesis.</t>
+          <t>Glide path to terminal. Analyst thesis input.</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1528,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Year-10 EBIT margin; current margin is the start.</t>
+          <t>Sourced from industry feed; override for thesis upside/downside.</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1558,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Reinvestment = ΔRevenue / S2C. Lower = more capital intensive.</t>
+          <t>Sourced from industry feed when available.</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1578,12 @@
           <t>Terminal growth rate (perpetuity)</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="10" t="n">
         <v>0.042</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Capped at risk-free rate.</t>
+          <t>Capped at risk-free rate. Analyst input.</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1598,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Converges to mature-firm WACC.</t>
+          <t>Sourced from industry feed (industry WACC); converges to mature-firm.</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1613,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Sustainable competitive return.</t>
+          <t>Sourced from industry feed; sustainable competitive return.</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2441,7 @@
           <t>Operating margin</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n"/>
+      <c r="B4" s="8" t="n"/>
       <c r="C4" s="22">
         <f>IFERROR(IF(1&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*1),"")</f>
         <v/>

--- a/templates/valuation_template.xlsx
+++ b/templates/valuation_template.xlsx
@@ -23,9 +23,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="166" formatCode="_($* #,##0_);_($* (#,##0);_($* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_($* #,##0_);_($* (#,##0);_($* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
@@ -47,12 +47,12 @@
     <font/>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -73,22 +73,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,31 +134,35 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -261,6 +265,36 @@
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
         <t>Pipeline field: meta.source</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: forward_guidance.period</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: forward_guidance.revenue_low</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: forward_guidance.revenue_high</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: forward_guidance.operating_income_low</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: forward_guidance.operating_income_high</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: forward_guidance.notes</t>
       </text>
     </comment>
   </commentList>
@@ -1151,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1214,144 +1248,260 @@
       <c r="B8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Two-stage FCFF DCF. Explicit 10-year forecast → terminal value via stable-growth Gordon. Operating leases treated as debt (post-ASC 842).</t>
-        </is>
-      </c>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Forward Guidance (latest earnings release)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Cell color legend</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr"/>
+          <t>Revenue, low ($M)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Yellow</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Analyst input — tunable</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Revenue, high ($M)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Green</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Pipeline-populated (sourced from filings/data room)</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Operating income, low ($M)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  White</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Computed (formula)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Operating income, high ($M)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Sheets</t>
-        </is>
-      </c>
+      <c r="A16" s="5" t="inlineStr"/>
       <c r="B16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Inputs</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Tunable assumptions + balance-sheet bridge items</t>
-        </is>
-      </c>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Forecast vs guidance (sanity)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Historicals</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>3 years of P&amp;L + cash flow + capex</t>
-        </is>
+          <t xml:space="preserve">  Y1 forecast revenue</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>Forecast!C3</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Segments</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Revenue &amp; operating income by reportable segment</t>
-        </is>
+          <t xml:space="preserve">  Implied Q-avg ($M, Y1 / 4)</t>
+        </is>
+      </c>
+      <c r="B19" s="9">
+        <f>Forecast!C3/4</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Forecast</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>10-year FCFF projection + terminal year</t>
-        </is>
+          <t xml:space="preserve">  Guidance revenue midpoint</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>IFERROR((B11+B12)/2,"")</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Implied Q-avg / guidance midpoint</t>
+        </is>
+      </c>
+      <c r="B21" s="10">
+        <f>IFERROR(B19/B20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Two-stage FCFF DCF. Explicit 10-year forecast → terminal value via stable-growth Gordon. Operating leases treated as debt (post-ASC 842).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Cell color legend</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Yellow</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Analyst input — tunable</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Green</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Pipeline-populated (sourced from filings/data room)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  White</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Computed (formula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Inputs</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Tunable assumptions + balance-sheet bridge items</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Historicals</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>3 years of P&amp;L + cash flow + capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Segments</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Revenue &amp; operating income by reportable segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Forecast</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>10-year FCFF projection + terminal year</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  WACC</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Cost of capital build</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Sum-of-PV → equity value → value per share</t>
         </is>
@@ -1381,24 +1531,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>— Capital structure &amp; cost of capital —</t>
         </is>
@@ -1410,7 +1560,7 @@
           <t>Risk-free rate (10Y UST)</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="12" t="n">
         <v>0.042</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1425,7 +1575,7 @@
           <t>Equity risk premium (mature US)</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="12" t="n">
         <v>0.0475</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1440,7 +1590,7 @@
           <t>Levered beta</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="13" t="n">
         <v>1.1</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1455,7 +1605,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="12" t="n">
         <v>0.055</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1470,7 +1620,7 @@
           <t>Marginal tax rate</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="14" t="n">
         <v>0.25</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1485,7 +1635,7 @@
           <t>Effective tax rate (current)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
+      <c r="B8" s="12" t="n"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Provision / pre-tax income — pipeline pulls from filing.</t>
@@ -1493,10 +1643,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>— Operating story —</t>
         </is>
@@ -1508,7 +1658,7 @@
           <t>Compounded revenue growth, Y1-Y5</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="14" t="n">
         <v>0.08</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1523,7 +1673,7 @@
           <t>Target pre-tax operating margin (Y10)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1538,7 +1688,7 @@
           <t>Year margins reach target</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="15" t="n">
         <v>5</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1553,7 +1703,7 @@
           <t>Sales-to-capital ratio (reinvestment)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="16" t="n">
         <v>1.5</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1563,10 +1713,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>— Terminal-year assumptions —</t>
         </is>
@@ -1578,7 +1728,7 @@
           <t>Terminal growth rate (perpetuity)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="14" t="n">
         <v>0.042</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1593,7 +1743,7 @@
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="12" t="n">
         <v>0.075</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1608,7 +1758,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="12" t="n">
         <v>0.12</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1618,10 +1768,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr"/>
+      <c r="A20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>— Balance sheet add-backs (pipeline-populated) —</t>
         </is>
@@ -1633,7 +1783,7 @@
           <t>Cash &amp; cash equivalents</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
+      <c r="B22" s="17" t="n"/>
       <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Most recent balance sheet.</t>
@@ -1646,7 +1796,7 @@
           <t>Marketable securities</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
+      <c r="B23" s="17" t="n"/>
       <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Most recent balance sheet.</t>
@@ -1659,7 +1809,7 @@
           <t>Long-term debt</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
+      <c r="B24" s="17" t="n"/>
       <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Most recent balance sheet.</t>
@@ -1672,7 +1822,7 @@
           <t>Long-term lease liabilities (treated as debt)</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
+      <c r="B25" s="17" t="n"/>
       <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Post-ASC 842; on balance sheet.</t>
@@ -1685,7 +1835,7 @@
           <t>Shares outstanding (millions)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
+      <c r="B26" s="18" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Most recent count from cover page.</t>
@@ -1715,22 +1865,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Line item ($M)</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>FY-2</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>FY-1</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>FY (latest)</t>
         </is>
@@ -1742,9 +1892,9 @@
           <t>Net sales</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n"/>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1752,9 +1902,9 @@
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1762,9 +1912,9 @@
           <t>Fulfillment</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1772,9 +1922,9 @@
           <t>Technology and infrastructure</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1782,9 +1932,9 @@
           <t>Sales and marketing</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1792,9 +1942,9 @@
           <t>General and administrative</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1802,29 +1952,29 @@
           <t>Other operating expense</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Operating income</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1832,9 +1982,9 @@
           <t>Interest income</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1842,9 +1992,9 @@
           <t>Interest expense</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1852,9 +2002,9 @@
           <t>Other income (expense), net</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1862,9 +2012,9 @@
           <t>Income before tax</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1872,35 +2022,35 @@
           <t>Provision for tax</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Operating margin</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="10">
         <f>IFERROR(B10/B2,"")</f>
         <v/>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="10">
         <f>IFERROR(C10/C2,"")</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="10">
         <f>IFERROR(D10/D2,"")</f>
         <v/>
       </c>
@@ -1911,9 +2061,9 @@
           <t>Capex (PP&amp;E purchases, net)</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1921,19 +2071,19 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1958,276 +2108,276 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Segment</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>FY-2</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>FY-1</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>FY (latest)</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>YoY growth</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Net sales by segment ($M)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="n"/>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="16">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="10">
         <f>IFERROR(D3/C3-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n"/>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="16">
+      <c r="A4" s="20" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="10">
         <f>IFERROR(D4/C4-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="16">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="10">
         <f>IFERROR(D5/C5-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n"/>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="16">
+      <c r="A6" s="20" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="10">
         <f>IFERROR(D6/C6-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n"/>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="16">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="10">
         <f>IFERROR(D7/C7-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="21">
         <f>SUM(B3:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="21">
         <f>SUM(C3:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="21">
         <f>SUM(D3:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="22">
         <f>IFERROR(D8/C8-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Operating income by segment ($M)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20">
+      <c r="A11" s="23">
         <f>A3</f>
         <v/>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20">
+      <c r="A12" s="23">
         <f>A4</f>
         <v/>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="20">
+      <c r="A13" s="23">
         <f>A5</f>
         <v/>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20">
+      <c r="A14" s="23">
         <f>A6</f>
         <v/>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="20">
+      <c r="A15" s="23">
         <f>A7</f>
         <v/>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="21">
         <f>SUM(B11:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="21">
         <f>SUM(C11:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="21">
         <f>SUM(D11:D15)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Operating margin by segment</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20">
+      <c r="A19" s="23">
         <f>A3</f>
         <v/>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="10">
         <f>IFERROR(B11/B3,"")</f>
         <v/>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="10">
         <f>IFERROR(C11/C3,"")</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="10">
         <f>IFERROR(D11/D3,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20">
+      <c r="A20" s="23">
         <f>A4</f>
         <v/>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="10">
         <f>IFERROR(B12/B4,"")</f>
         <v/>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="10">
         <f>IFERROR(C12/C4,"")</f>
         <v/>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="10">
         <f>IFERROR(D12/D4,"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20">
+      <c r="A21" s="23">
         <f>A5</f>
         <v/>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="10">
         <f>IFERROR(B13/B5,"")</f>
         <v/>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="10">
         <f>IFERROR(C13/C5,"")</f>
         <v/>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="10">
         <f>IFERROR(D13/D5,"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20">
+      <c r="A22" s="23">
         <f>A6</f>
         <v/>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="10">
         <f>IFERROR(B14/B6,"")</f>
         <v/>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="10">
         <f>IFERROR(C14/C6,"")</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="10">
         <f>IFERROR(D14/D6,"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20">
+      <c r="A23" s="23">
         <f>A7</f>
         <v/>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="10">
         <f>IFERROR(B15/B7,"")</f>
         <v/>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="10">
         <f>IFERROR(C15/C7,"")</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="10">
         <f>IFERROR(D15/D7,"")</f>
         <v/>
       </c>
@@ -2265,67 +2415,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Line item ($M)</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Base (FY latest)</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Y7</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Y8</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Y9</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Y10</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Terminal</t>
         </is>
@@ -2337,48 +2487,48 @@
           <t>Revenue growth rate</t>
         </is>
       </c>
-      <c r="B2" s="21" t="n"/>
-      <c r="C2" s="22">
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="25">
         <f>Inputs!B11</f>
         <v/>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="25">
         <f>Inputs!B11</f>
         <v/>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="25">
         <f>Inputs!B11</f>
         <v/>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="25">
         <f>Inputs!B11</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="25">
         <f>Inputs!B11</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="25">
         <f>Inputs!B11-((Inputs!B11-Inputs!B17)/5)*1</f>
         <v/>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="25">
         <f>Inputs!B11-((Inputs!B11-Inputs!B17)/5)*2</f>
         <v/>
       </c>
-      <c r="J2" s="22">
+      <c r="J2" s="25">
         <f>Inputs!B11-((Inputs!B11-Inputs!B17)/5)*3</f>
         <v/>
       </c>
-      <c r="K2" s="22">
+      <c r="K2" s="25">
         <f>Inputs!B11-((Inputs!B11-Inputs!B17)/5)*4</f>
         <v/>
       </c>
-      <c r="L2" s="22">
+      <c r="L2" s="25">
         <f>Inputs!B11-((Inputs!B11-Inputs!B17)/5)*5</f>
         <v/>
       </c>
-      <c r="M2" s="22">
+      <c r="M2" s="25">
         <f>Inputs!B17</f>
         <v/>
       </c>
@@ -2389,48 +2539,48 @@
           <t>Revenues</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="23">
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="9">
         <f>IFERROR(B3*(1+C2),"")</f>
         <v/>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="9">
         <f>IFERROR(C3*(1+D2),"")</f>
         <v/>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="9">
         <f>IFERROR(D3*(1+E2),"")</f>
         <v/>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="9">
         <f>IFERROR(E3*(1+F2),"")</f>
         <v/>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="9">
         <f>IFERROR(F3*(1+G2),"")</f>
         <v/>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="9">
         <f>IFERROR(G3*(1+H2),"")</f>
         <v/>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="9">
         <f>IFERROR(H3*(1+I2),"")</f>
         <v/>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="9">
         <f>IFERROR(I3*(1+J2),"")</f>
         <v/>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="9">
         <f>IFERROR(J3*(1+K2),"")</f>
         <v/>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="9">
         <f>IFERROR(K3*(1+L2),"")</f>
         <v/>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="9">
         <f>IFERROR(L3*(1+M2),"")</f>
         <v/>
       </c>
@@ -2441,48 +2591,48 @@
           <t>Operating margin</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="22">
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="25">
         <f>IFERROR(IF(1&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*1),"")</f>
         <v/>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="25">
         <f>IFERROR(IF(2&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*2),"")</f>
         <v/>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <f>IFERROR(IF(3&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*3),"")</f>
         <v/>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="25">
         <f>IFERROR(IF(4&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*4),"")</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="25">
         <f>IFERROR(IF(5&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*5),"")</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="25">
         <f>IFERROR(IF(6&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*6),"")</f>
         <v/>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="25">
         <f>IFERROR(IF(7&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*7),"")</f>
         <v/>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="25">
         <f>IFERROR(IF(8&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*8),"")</f>
         <v/>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="25">
         <f>IFERROR(IF(9&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*9),"")</f>
         <v/>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="25">
         <f>IFERROR(IF(10&gt;Inputs!B13,Inputs!B12,$B$4+((Inputs!B12-$B$4)/Inputs!B13)*10),"")</f>
         <v/>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="25">
         <f>Inputs!B12</f>
         <v/>
       </c>
@@ -2493,51 +2643,51 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="9">
         <f>IFERROR(B3*B4,"")</f>
         <v/>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="9">
         <f>IFERROR(C3*C4,"")</f>
         <v/>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="9">
         <f>IFERROR(D3*D4,"")</f>
         <v/>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="9">
         <f>IFERROR(E3*E4,"")</f>
         <v/>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="9">
         <f>IFERROR(F3*F4,"")</f>
         <v/>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="9">
         <f>IFERROR(G3*G4,"")</f>
         <v/>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="9">
         <f>IFERROR(H3*H4,"")</f>
         <v/>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="9">
         <f>IFERROR(I3*I4,"")</f>
         <v/>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="9">
         <f>IFERROR(J3*J4,"")</f>
         <v/>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="9">
         <f>IFERROR(K3*K4,"")</f>
         <v/>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="9">
         <f>IFERROR(L3*L4,"")</f>
         <v/>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="9">
         <f>IFERROR(M3*M4,"")</f>
         <v/>
       </c>
@@ -2548,51 +2698,51 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="25">
         <f>Inputs!B8</f>
         <v/>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*1,"")</f>
         <v/>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*2,"")</f>
         <v/>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*3,"")</f>
         <v/>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*4,"")</f>
         <v/>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*5,"")</f>
         <v/>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*6,"")</f>
         <v/>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*7,"")</f>
         <v/>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*8,"")</f>
         <v/>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*9,"")</f>
         <v/>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="25">
         <f>IFERROR(Inputs!B8+((Inputs!B7-Inputs!B8)/10)*10,"")</f>
         <v/>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="25">
         <f>Inputs!B7</f>
         <v/>
       </c>
@@ -2603,51 +2753,51 @@
           <t>EBIT(1-t)</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="9">
         <f>IFERROR(B5*(1-B6),"")</f>
         <v/>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="9">
         <f>IFERROR(C5*(1-C6),"")</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="9">
         <f>IFERROR(D5*(1-D6),"")</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="9">
         <f>IFERROR(E5*(1-E6),"")</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="9">
         <f>IFERROR(F5*(1-F6),"")</f>
         <v/>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="9">
         <f>IFERROR(G5*(1-G6),"")</f>
         <v/>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="9">
         <f>IFERROR(H5*(1-H6),"")</f>
         <v/>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="9">
         <f>IFERROR(I5*(1-I6),"")</f>
         <v/>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="9">
         <f>IFERROR(J5*(1-J6),"")</f>
         <v/>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="9">
         <f>IFERROR(K5*(1-K6),"")</f>
         <v/>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="9">
         <f>IFERROR(L5*(1-L6),"")</f>
         <v/>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="9">
         <f>IFERROR(M5*(1-M6),"")</f>
         <v/>
       </c>
@@ -2658,98 +2808,98 @@
           <t>Reinvestment (ΔRev / S2C)</t>
         </is>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="9">
         <f>IFERROR((C3-B3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="9">
         <f>IFERROR((D3-C3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="9">
         <f>IFERROR((E3-D3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="9">
         <f>IFERROR((F3-E3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="9">
         <f>IFERROR((G3-F3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="9">
         <f>IFERROR((H3-G3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="9">
         <f>IFERROR((I3-H3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="9">
         <f>IFERROR((J3-I3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="9">
         <f>IFERROR((K3-J3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="9">
         <f>IFERROR((L3-K3)/Inputs!B14,"")</f>
         <v/>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="9">
         <f>IFERROR(M7*(Inputs!B17/Inputs!B19),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="21">
         <f>IFERROR(C7-C8,"")</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="21">
         <f>IFERROR(D7-D8,"")</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="21">
         <f>IFERROR(E7-E8,"")</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="21">
         <f>IFERROR(F7-F8,"")</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="21">
         <f>IFERROR(G7-G8,"")</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="21">
         <f>IFERROR(H7-H8,"")</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="21">
         <f>IFERROR(I7-I8,"")</f>
         <v/>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="21">
         <f>IFERROR(J7-J8,"")</f>
         <v/>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="21">
         <f>IFERROR(K7-K8,"")</f>
         <v/>
       </c>
-      <c r="L9" s="18">
+      <c r="L9" s="21">
         <f>IFERROR(L7-L8,"")</f>
         <v/>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="21">
         <f>IFERROR(M7-M8,"")</f>
         <v/>
       </c>
@@ -2760,47 +2910,47 @@
           <t>Cost of capital (WACC)</t>
         </is>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="25">
         <f>WACC!B14</f>
         <v/>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="25">
         <f>WACC!B14</f>
         <v/>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="25">
         <f>WACC!B14</f>
         <v/>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="25">
         <f>WACC!B14</f>
         <v/>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="25">
         <f>WACC!B14</f>
         <v/>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="25">
         <f>WACC!B14-((WACC!B14-Inputs!B18)/5)*1</f>
         <v/>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="25">
         <f>WACC!B14-((WACC!B14-Inputs!B18)/5)*2</f>
         <v/>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="25">
         <f>WACC!B14-((WACC!B14-Inputs!B18)/5)*3</f>
         <v/>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="25">
         <f>WACC!B14-((WACC!B14-Inputs!B18)/5)*4</f>
         <v/>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="25">
         <f>WACC!B14-((WACC!B14-Inputs!B18)/5)*5</f>
         <v/>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="25">
         <f>Inputs!B18</f>
         <v/>
       </c>
@@ -2811,43 +2961,43 @@
           <t>Cumulative discount factor</t>
         </is>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <f>1/(1+C10)</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="27">
         <f>C11*(1/(1+D10))</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="27">
         <f>D11*(1/(1+E10))</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="27">
         <f>E11*(1/(1+F10))</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="27">
         <f>F11*(1/(1+G10))</f>
         <v/>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="27">
         <f>G11*(1/(1+H10))</f>
         <v/>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="27">
         <f>H11*(1/(1+I10))</f>
         <v/>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="27">
         <f>I11*(1/(1+J10))</f>
         <v/>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="27">
         <f>J11*(1/(1+K10))</f>
         <v/>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="27">
         <f>K11*(1/(1+L10))</f>
         <v/>
       </c>
@@ -2858,43 +3008,43 @@
           <t>PV(FCFF)</t>
         </is>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="9">
         <f>IFERROR(C9*C11,"")</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="9">
         <f>IFERROR(D9*D11,"")</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="9">
         <f>IFERROR(E9*E11,"")</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="9">
         <f>IFERROR(F9*F11,"")</f>
         <v/>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="9">
         <f>IFERROR(G9*G11,"")</f>
         <v/>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="9">
         <f>IFERROR(H9*H11,"")</f>
         <v/>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="9">
         <f>IFERROR(I9*I11,"")</f>
         <v/>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="9">
         <f>IFERROR(J9*J11,"")</f>
         <v/>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="9">
         <f>IFERROR(K9*K11,"")</f>
         <v/>
       </c>
-      <c r="L12" s="23">
+      <c r="L12" s="9">
         <f>IFERROR(L9*L11,"")</f>
         <v/>
       </c>
@@ -2920,24 +3070,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>WACC build</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Cost of equity</t>
         </is>
@@ -2949,7 +3099,7 @@
           <t>Risk-free rate</t>
         </is>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="22">
         <f>Inputs!B3</f>
         <v/>
       </c>
@@ -2960,7 +3110,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="28">
         <f>Inputs!B5</f>
         <v/>
       </c>
@@ -2971,7 +3121,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="22">
         <f>Inputs!B4</f>
         <v/>
       </c>
@@ -2982,13 +3132,13 @@
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="29">
         <f>B3+B4*B5</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Cost of debt</t>
         </is>
@@ -3000,7 +3150,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="22">
         <f>Inputs!B6</f>
         <v/>
       </c>
@@ -3011,7 +3161,7 @@
           <t>Marginal tax rate</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="22">
         <f>Inputs!B7</f>
         <v/>
       </c>
@@ -3022,25 +3172,25 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="22">
         <f>B9*(1-B10)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Capital structure</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="29">
         <f>IF(ISNUMBER(B15),(B15/(B15+(Inputs!B24+Inputs!B25)))*B6 + ((Inputs!B24+Inputs!B25)/(B15+(Inputs!B24+Inputs!B25)))*B11,0.7*B6 + 0.3*B11)</f>
         <v/>
       </c>
@@ -3056,7 +3206,7 @@
           <t>Market cap (override) — for market WACC</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
+      <c r="B15" s="17" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Pipeline-populated. If blank, falls back to 70/30 default split.</t>
@@ -3084,17 +3234,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Valuation output</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Value ($M)</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3106,7 +3256,7 @@
           <t>Sum of PV(FCFF), Y1-Y10</t>
         </is>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="9">
         <f>SUM(Forecast!C12:L12)</f>
         <v/>
       </c>
@@ -3117,7 +3267,7 @@
           <t>Terminal FCFF (Y11)</t>
         </is>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="9">
         <f>Forecast!M9</f>
         <v/>
       </c>
@@ -3128,7 +3278,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="9">
         <f>IFERROR(B3/(Inputs!B18-Inputs!B17),"")</f>
         <v/>
       </c>
@@ -3139,7 +3289,7 @@
           <t>PV(Terminal value)</t>
         </is>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="9">
         <f>IFERROR(B4*Forecast!L11,"")</f>
         <v/>
       </c>
@@ -3150,13 +3300,13 @@
           <t>Enterprise value (operating)</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="21">
         <f>B2+B5</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Bridge to equity value</t>
         </is>
@@ -3168,7 +3318,7 @@
           <t>(-) Long-term debt</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="9">
         <f>-Inputs!B24</f>
         <v/>
       </c>
@@ -3179,7 +3329,7 @@
           <t>(-) Long-term lease liabilities</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="9">
         <f>-Inputs!B25</f>
         <v/>
       </c>
@@ -3190,7 +3340,7 @@
           <t>(+) Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="9">
         <f>Inputs!B22</f>
         <v/>
       </c>
@@ -3201,7 +3351,7 @@
           <t>(+) Marketable securities</t>
         </is>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="9">
         <f>Inputs!B23</f>
         <v/>
       </c>
@@ -3212,7 +3362,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="21">
         <f>B6+B9+B10+B11+B12</f>
         <v/>
       </c>
@@ -3223,7 +3373,7 @@
           <t>Shares outstanding (M)</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="30">
         <f>Inputs!B26</f>
         <v/>
       </c>
@@ -3234,13 +3384,13 @@
           <t>Implied value per share ($)</t>
         </is>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="31">
         <f>IFERROR(B13/B15,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Sanity check vs market</t>
         </is>
@@ -3252,7 +3402,7 @@
           <t>Current market price ($/share)</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n"/>
+      <c r="B19" s="32" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3260,7 +3410,7 @@
           <t>Implied / Market</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="22">
         <f>IFERROR(B16/B19,"")</f>
         <v/>
       </c>

--- a/templates/valuation_template.xlsx
+++ b/templates/valuation_template.xlsx
@@ -295,6 +295,81 @@
     <comment ref="B15" authorId="0" shapeId="0">
       <text>
         <t>Pipeline field: forward_guidance.notes</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[0].description</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[0].period</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[0].line_item</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[0].amount</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[0].source_quote</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[1].description</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[1].period</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[1].line_item</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[1].amount</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[1].source_quote</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[2].description</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[2].period</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[2].line_item</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[2].amount</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>Pipeline field: non_recurring_items[2].source_quote</t>
       </text>
     </comment>
   </commentList>
@@ -1185,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1364,144 +1439,321 @@
       <c r="B22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Two-stage FCFF DCF. Explicit 10-year forecast → terminal value via stable-growth Gordon. Operating leases treated as debt (post-ASC 842).</t>
-        </is>
-      </c>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Non-recurring items (carved out for normalization)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="4" t="inlineStr"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  #1 Description</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Cell color legend</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  #1 Period</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Yellow</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Analyst input — tunable</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  #1 Line item</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Green</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Pipeline-populated (sourced from filings/data room)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+          <t xml:space="preserve">  #1 Amount ($M)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28" ht="50" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  White</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Computed (formula)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  #1 Source quote</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="4" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  #2 Description</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Sheets</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  #2 Period</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Inputs</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Tunable assumptions + balance-sheet bridge items</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  #2 Line item</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Historicals</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>3 years of P&amp;L + cash flow + capex</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+          <t xml:space="preserve">  #2 Amount ($M)</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33" ht="50" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Segments</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Revenue &amp; operating income by reportable segment</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  #2 Source quote</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Forecast</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>10-year FCFF projection + terminal year</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  #3 Description</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WACC</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Cost of capital build</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  #3 Period</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  #3 Line item</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  #3 Amount ($M)</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38" ht="50" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  #3 Source quote</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Other income normalization</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other income (as-reported)</t>
+        </is>
+      </c>
+      <c r="B41" s="9">
+        <f>Historicals!D13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-recurring items, sum</t>
+        </is>
+      </c>
+      <c r="B42" s="9">
+        <f>SUM(B27,B32,B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Normalized Other income</t>
+        </is>
+      </c>
+      <c r="B43" s="9">
+        <f>B41-B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Two-stage FCFF DCF. Explicit 10-year forecast → terminal value via stable-growth Gordon. Operating leases treated as debt (post-ASC 842).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr"/>
+      <c r="B46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Cell color legend</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Yellow</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Analyst input — tunable</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Green</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Pipeline-populated (sourced from filings/data room)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  White</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Computed (formula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Inputs</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Tunable assumptions + balance-sheet bridge items</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Historicals</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>3 years of P&amp;L + cash flow + capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Segments</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Revenue &amp; operating income by reportable segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Forecast</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>10-year FCFF projection + terminal year</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WACC</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Cost of capital build</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Valuation</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Sum-of-PV → equity value → value per share</t>
         </is>
